--- a/refer_file/sources.xlsx
+++ b/refer_file/sources.xlsx
@@ -1252,19 +1252,23 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>(chưa có nguồn — chạy discover_sources.py)</t>
+          <t>refer_file/_discovered/</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:23:04.024106+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5282,7 +5286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O211"/>
+  <dimension ref="A1:O227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17766,6 +17770,1142 @@
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Overview – Shanghai Hongqiao Intl CBD (official)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://en.shhqcbd.gov.cn/overview.html</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Lấy tổng quan chính thức: diện tích 151,4 km², mô hình quy hoạch "1+4", định vị 4 phân khu và website chính thức của khu.</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>case_name;aerotropolis;country;airport_name;reference_city;official_website;area_km2;positioning;planning_concept;cornerstones;subzones;vision_label;vision_qualities</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L212" t="n">
+        <v>200</v>
+      </c>
+      <c r="M212" t="n">
+        <v>3678</v>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>pages/01_overview_shanghai_hongqiao_intl_cbd_official.txt</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:20:26.584964+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Overview of Shanghai Hongqiao International CBD</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>http://en.shhqcbd.gov.cn/2024-05/24/c_990100.htm</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Lấy diện tích chi tiết từng phân khu (Nam/Đông/Tây/Bắc Hongqiao), định vị thương mại – hội chợ và vai trò hub giao thông tổng hợp.</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>area_km2;subzones;positioning;location_desc;connectivity_desc;connection_modes;development_context</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L213" t="n">
+        <v>200</v>
+      </c>
+      <c r="M213" t="n">
+        <v>3659</v>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>pages/02_overview_of_shanghai_hongqiao_international_cbd.txt</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:20:33.308213+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>3</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Development plan for Hongqiao Intl CBD and surrounding areas</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>http://en.shhqcbd.gov.cn/2025-09/12/c_1125212.htm</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Lấy quy hoạch tổng thể mới (535 km², "một lõi – hai trục – bốn khu – năm vành đai xanh"), mục tiêu 2035 và chỉ tiêu tiếp cận metro 600 m.</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>planning_concept;subzones;cornerstones;vision_label;vision_qualities;sustainability;positioning;metro_lines</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L214" t="n">
+        <v>200</v>
+      </c>
+      <c r="M214" t="n">
+        <v>5899</v>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>pages/03_development_plan_for_hongqiao_intl_cbd_and_surroun.txt</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:20:40.425031+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>4</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Hongqiao transportation hub becomes the world's busiest</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>https://en.shhqcbd.gov.cn/2026-03/19/c_1170683.htm</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Lấy số liệu kết nối đa phương thức: 422 triệu lượt khách qua hub, 50 triệu khách sân bay 2025, 155 triệu khách ga HSR, mạng lưới HSR 6 hướng.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>passengers_million;connectivity_desc;connection_modes;rail_connections;metro_lines;cvp_convenience;experience_desc</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>200</v>
+      </c>
+      <c r="M215" t="n">
+        <v>3266</v>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>pages/04_hongqiao_transportation_hub_becomes_the_world_s_bu.txt</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:20:52.774380+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>5</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Hongqiao Intl CBD economic performance 2025</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>http://en.shhqcbd.gov.cn/2026-02/09/c_1160377.htm</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Lấy số doanh nghiệp (283 trụ sở cấp thành phố, &gt;7.000 DN kinh tế số), kim ngạch ngoại thương và vốn FDI thực hiện của khu.</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>num_companies_realestate;num_companies_airport;total_investment_usd;development_context;economic_zone_name</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L216" t="n">
+        <v>200</v>
+      </c>
+      <c r="M216" t="n">
+        <v>4051</v>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>pages/05_hongqiao_intl_cbd_economic_performance_2025.txt</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:20:56.632403+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>6</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>New Hongqiao Pinhui building set for operation</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>http://en.shhqcbd.gov.cn/2024-11/04/c_1043634.htm</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Lấy dữ liệu khu thương mại chuyên biệt Hongqiao Pinhui (Trung tâm trưng bày &amp; giao dịch hàng nhập khẩu): diện tích 130.000 m², chức năng, thời điểm vận hành.</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>trade_park_name;trade_park_ha;commercial_re;cvp_product;highlight_amenities;brand_partners</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L217" t="n">
+        <v>200</v>
+      </c>
+      <c r="M217" t="n">
+        <v>3584</v>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>pages/06_new_hongqiao_pinhui_building_set_for_operation.txt</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:20:59.490527+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>7</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Shanghai Airport Authority – record passenger &amp; cargo volumes</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.shanghaiairport.com/ensh/xwg/info_itemid_43826.html</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Lấy số liệu chính thức từ nhà khai thác sân bay: Hongqiao vượt 50 triệu khách 2025, tổng hàng hóa và cất/hạ cánh của hệ thống sân bay Thượng Hải.</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>passengers_million;cargo_million_tonnes;air_movements</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L218" t="n">
+        <v>200</v>
+      </c>
+      <c r="M218" t="n">
+        <v>5421</v>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>pages/07_shanghai_airport_authority_record_passenger_cargo_.txt</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:21:03.566263+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>8</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Shanghai Government – Hongqiao International CBD (National Development Zone)</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://english.shanghai.gov.cn/en-NationalDevelopmentZone/20231211/ecf9d8dc8b544a29af71c9c5bb858676.html</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Lấy dữ liệu chính quyền thành phố: 86 km² lõi + 64,8 km² mở rộng, diện tích và ngành trọng điểm của từng phân khu.</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>area_km2;subzones;positioning;cornerstones;location_desc;investor_governance</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L219" t="n">
+        <v>200</v>
+      </c>
+      <c r="M219" t="n">
+        <v>7112</v>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>pages/08_shanghai_government_hongqiao_international_cbd_nat.txt</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:21:25.256085+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>9</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Invest Shanghai – Hongqiao Central Business District policies</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.investsh.org.cn/invest/policy/en/view/D3EFFB73-594E-4D3C-B4F2-FFD553A4365E</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Lấy chính sách ưu đãi và cơ chế giá/hỗ trợ: quỹ phát triển 2 tỷ RMB, trợ giá thuê văn phòng 3 năm, trợ cấp trụ sở, ngành khuyến khích.</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>cvp_price;cvp_price_note;sales_scheme;investor_governance;gov_led_ratio_pct;economic_zone_name;positioning;cvp_service</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L220" t="n">
+        <v>200</v>
+      </c>
+      <c r="M220" t="n">
+        <v>9226</v>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>pages/09_invest_shanghai_hongqiao_central_business_district.txt</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:22:08.779237+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>10</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Urban planning in Hongqiao CBD puts sustainability front and center</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://english.shanghai.gov.cn/en-ForumHighlights/20250529/4c7a3882ef034784ba78bc797b216059.html</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Lấy dữ liệu bền vững &amp; thành phố thông minh: giảm 58% phát thải, 13 dự án/2,12 triệu m² đạt LEED, hệ thống cấp nhiệt–lạnh–điện tập trung, 24 hầm đi bộ và 13 cầu trên cao.</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>sustainability;smart_city;has_smart_city;cvp_experience;experience_desc;num_office_buildings;founded_year;planning_concept</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L221" t="n">
+        <v>200</v>
+      </c>
+      <c r="M221" t="n">
+        <v>11422</v>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>pages/10_urban_planning_in_hongqiao_cbd_puts_sustainability.txt</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:22:22.020728+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>11</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Why Hongqiao CBD – China Daily chuyên trang Hongqiao CBD</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://regional.chinadaily.com.cn/hongqiaocbd/2016-03/31/c_50614.htm</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Lấy bối cảnh phát triển, khái niệm quy hoạch (khu trình diễn thành phố thông minh &amp; phát thải thấp) và tổng vốn hạ tầng &gt;100 tỷ NDT (~15,3 tỷ USD).</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>total_investment_usd;development_context;planning_concept;positioning;smart_city;urban_build_period</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L222" t="n">
+        <v>200</v>
+      </c>
+      <c r="M222" t="n">
+        <v>2890</v>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>pages/11_why_hongqiao_cbd_china_daily_chuy_n_trang_hongqiao.txt</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:22:36.101782+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>12</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>CIIE – National Exhibition and Convention Center (Shanghai) venue</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://www.ciie.org/zbh/en/AboutUs/Venueen/</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Lấy dữ liệu tổ hợp tiện ích lớn nhất khu: NECC 1,47 triệu m² sàn, 400.000 m² triển lãm trong nhà, khoảng cách 1,5 km tới hub Hongqiao.</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>highlight_amenities;basic_amenities;cvp_experience;experience_desc;cvp_brand;brand_desc;distance_to_city_km</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L223" t="n">
+        <v>200</v>
+      </c>
+      <c r="M223" t="n">
+        <v>4682</v>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>pages/12_ciie_national_exhibition_and_convention_center_sha.txt</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:22:39.686645+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>13</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Wikipedia – Shanghai Hongqiao International Airport</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Shanghai_Hongqiao_International_Airport</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Đối chiếu chỉ số sân bay: 50,15 triệu khách, 282.692 lượt cất/hạ cánh, 445.265 tấn hàng, 25 hãng bay, 63 điểm đến, 13 km tới trung tâm, khai trương 1929.</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>passengers_million;cargo_million_tonnes;air_movements;destinations;airlines;distance_to_city_km;airport_build_period;metro_lines;rail_connections</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L224" t="n">
+        <v>200</v>
+      </c>
+      <c r="M224" t="n">
+        <v>42656</v>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>pages/13_wikipedia_shanghai_hongqiao_international_airport.txt</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:22:45.932567+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>14</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Wikipedia – Hongqiao transportation hub</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hongqiao_transportation_hub</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Đối chiếu lịch sử xây dựng hub (đề xuất 2005, hoàn thành 2009, vận hành trước Expo 2010) và chủ đầu tư Shanghai Shen-Hong (Rainbow) Investment Corp.</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>airport_build_period;urban_build_period;founded_year;lead_developer;investor_governance;connection_modes;metro_lines;rail_connections</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L225" t="n">
+        <v>200</v>
+      </c>
+      <c r="M225" t="n">
+        <v>8564</v>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>pages/14_wikipedia_hongqiao_transportation_hub.txt</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:22:49.165597+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>15</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Wikipedia – Shanghai Hongqiao railway station</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Shanghai_Hongqiao_railway_station</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Đối chiếu dữ liệu ga HSR trong hub: khai trương 2010, 1,3 triệu m², 41 ke ga, 5 tuyến cao tốc, 210.000 khách/ngày, vốn đầu tư &gt;15 tỷ NDT.</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>rail_connections;connection_modes;metro_lines;total_investment_usd;urban_build_period;cvp_convenience;connectivity_desc</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L226" t="n">
+        <v>200</v>
+      </c>
+      <c r="M226" t="n">
+        <v>24935</v>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>pages/15_wikipedia_shanghai_hongqiao_railway_station.txt</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:22:51.589780+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>shanghai_hongqiao</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>16</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Airport Technology – Shanghai Hongqiao airport project profile</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.airport-technology.com/projects/shanghai-hongiao/</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Đối chiếu quy mô hạ tầng sân bay: diện tích 332.000 m², T1 82.000 m², T2 250.000 m², vốn mở rộng 15,3 tỷ NDT (2,2 tỷ USD), 2 đường băng.</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>airport_area_ha;total_investment_usd;airport_build_period;airport_privilege;has_airport_privilege</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>2026-08-19T16:12:07+0700</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L227" t="n">
+        <v>200</v>
+      </c>
+      <c r="M227" t="n">
+        <v>18861</v>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>pages/16_airport_technology_shanghai_hongqiao_airport_proje.txt</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>2026-08-19T09:22:54.143779+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
